--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486967_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486967_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2799</v>
+        <v>5.0307</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1639</v>
+        <v>7.2525</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.884</v>
+        <v>-2.2218</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1373</v>
+        <v>1.0908</v>
       </c>
       <c r="H2" t="n">
-        <v>0.772</v>
+        <v>0.5226</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3653</v>
+        <v>0.5682</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8648</v>
+        <v>3.124</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8527</v>
+        <v>0.7694</v>
       </c>
       <c r="L2" t="n">
-        <v>5.0122</v>
+        <v>2.3545</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.7275</v>
+        <v>-2.0332</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0807</v>
+        <v>-0.2468</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6468</v>
+        <v>-1.7863</v>
       </c>
       <c r="P2" t="n">
+        <v>1.2321</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-0.2053</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1077</v>
+        <v>0.831</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1122</v>
+        <v>0.5578</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0046</v>
+        <v>0.2732</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2402</v>
+        <v>1.8768</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2402</v>
+        <v>3.7761</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.8993</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1206</v>
+        <v>4.8967</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5203</v>
+        <v>5.5435</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3997</v>
+        <v>-0.6468</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0908</v>
+        <v>4.1373</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5226</v>
+        <v>0.772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5682</v>
+        <v>3.3653</v>
       </c>
       <c r="J3" t="n">
-        <v>3.124</v>
+        <v>6.8648</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7694</v>
+        <v>1.8527</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3545</v>
+        <v>5.0122</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0332</v>
+        <v>-2.7275</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2468</v>
+        <v>-1.0807</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7863</v>
+        <v>-1.6468</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2053</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.079</v>
+        <v>0.7245</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1744</v>
+        <v>0.4919</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0954</v>
+        <v>0.2326</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8768</v>
+        <v>0.2402</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7761</v>
+        <v>0.2402</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4787</v>
+        <v>2.248</v>
       </c>
       <c r="E4" t="n">
-        <v>7.083</v>
+        <v>3.0026</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.6043</v>
+        <v>-0.7546</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4166</v>
+        <v>-1.8344</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0638</v>
+        <v>-1.2685</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6472</v>
+        <v>-0.5659</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5424</v>
+        <v>0.2356</v>
       </c>
       <c r="K4" t="n">
-        <v>2.424</v>
+        <v>0.3149</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1184</v>
+        <v>-0.0793</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1258</v>
+        <v>-2.07</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3602</v>
+        <v>-1.5834</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.4866</v>
       </c>
       <c r="P4" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5014</v>
+        <v>1.8422</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2654</v>
+        <v>1.5535</v>
       </c>
       <c r="U4" t="n">
-        <v>0.236</v>
+        <v>0.2887</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.0554</v>
+        <v>1.4189</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4805</v>
+        <v>1.4189</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.5359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9137</v>
+        <v>1.2524</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7275</v>
+        <v>4.8863</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8139</v>
+        <v>-3.634</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8344</v>
+        <v>1.4166</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2685</v>
+        <v>2.0638</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5659</v>
+        <v>-0.6472</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2356</v>
+        <v>2.5424</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3149</v>
+        <v>2.424</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0793</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.07</v>
+        <v>-1.1258</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5834</v>
+        <v>-0.3602</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4866</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5078</v>
+        <v>2.2751</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2784</v>
+        <v>2.0688</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2294</v>
+        <v>0.2064</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4189</v>
+        <v>-3.0554</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4189</v>
+        <v>0.4805</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-3.5359</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0623</v>
+        <v>1.0012</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8168</v>
+        <v>2.7853</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7545</v>
+        <v>-1.7841</v>
       </c>
       <c r="G6" t="n">
         <v>0.4509</v>
@@ -922,13 +922,13 @@
         <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1043</v>
+        <v>1.0432</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1163</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2205</v>
+        <v>0.1909</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6982</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2803</v>
+        <v>0.1068</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6896</v>
+        <v>0.8988</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9698</v>
+        <v>-0.792</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2356</v>
@@ -1000,13 +1000,13 @@
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3394</v>
+        <v>0.7264</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4997</v>
+        <v>0.7089</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1604</v>
+        <v>0.0175</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4069</v>
+        <v>-1.061</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1911</v>
+        <v>1.8207</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.598</v>
+        <v>-2.8817</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3875</v>
+        <v>-1.3021</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1718</v>
+        <v>-1.0967</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2157</v>
+        <v>-0.2054</v>
       </c>
       <c r="J8" t="n">
-        <v>0.257</v>
+        <v>1.486</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2175</v>
+        <v>-0.2107</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0395</v>
+        <v>1.6967</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6445</v>
+        <v>-2.788</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3893</v>
+        <v>-0.886</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2552</v>
+        <v>-1.902</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0461</v>
+        <v>0.124</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0659</v>
+        <v>0.0309</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0198</v>
+        <v>0.0931</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1786</v>
+        <v>0.9384</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4545</v>
+        <v>-1.1446</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0937</v>
+        <v>-0.191</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3608</v>
+        <v>-0.9537</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2609</v>
@@ -1156,13 +1156,13 @@
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8332000000000001</v>
+        <v>1.143</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4457</v>
+        <v>0.457</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2788</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>1.1786</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7825</v>
+        <v>-1.3114</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3364</v>
+        <v>0.257</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1189</v>
+        <v>-1.5684</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3021</v>
+        <v>-0.3875</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0967</v>
+        <v>-0.1718</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2054</v>
+        <v>-0.2157</v>
       </c>
       <c r="J10" t="n">
-        <v>1.486</v>
+        <v>0.257</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2107</v>
+        <v>0.2175</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6967</v>
+        <v>0.0395</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.788</v>
+        <v>-0.6445</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.886</v>
+        <v>-0.3893</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.902</v>
+        <v>-0.2552</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5974</v>
+        <v>0.0494</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4534</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.144</v>
+        <v>0.0494</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9384</v>
+        <v>-1.1786</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5449</v>
+        <v>-2.6446</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6158</v>
+        <v>-0.8638</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9291</v>
+        <v>-1.7808</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7749</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>1.23</v>
+        <v>1.1303</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2707</v>
+        <v>1.0227</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0407</v>
+        <v>0.1075</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1786</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6584</v>
+        <v>-3.9877</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8654</v>
+        <v>-2.7797</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.793</v>
+        <v>-1.208</v>
       </c>
       <c r="G12" t="n">
         <v>-3.1282</v>
@@ -1390,13 +1390,13 @@
         <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4432</v>
+        <v>1.1139</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4411</v>
+        <v>0.5268</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0021</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>3.7761</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.727699999999999</v>
+        <v>4.386500000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>21.9537</v>
+        <v>22.6122</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.226</v>
+        <v>-18.2259</v>
       </c>
       <c r="G13" t="n">
         <v>-5.827999999999999</v>
@@ -1444,7 +1444,7 @@
         <v>17.2129</v>
       </c>
       <c r="K13" t="n">
-        <v>5.3883</v>
+        <v>5.388300000000001</v>
       </c>
       <c r="L13" t="n">
         <v>11.8245</v>
@@ -1468,13 +1468,13 @@
         <v>11.2939</v>
       </c>
       <c r="S13" t="n">
-        <v>10.3445</v>
+        <v>11.003</v>
       </c>
       <c r="T13" t="n">
-        <v>7.611799999999999</v>
+        <v>8.2706</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7323</v>
+        <v>2.7325</v>
       </c>
       <c r="V13" t="n">
         <v>3.3182</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6432</v>
+        <v>2.3521</v>
       </c>
       <c r="E14" t="n">
-        <v>6.055</v>
+        <v>5.2182</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.4118</v>
+        <v>-2.8661</v>
       </c>
       <c r="G14" t="n">
         <v>0.911</v>
@@ -1546,13 +1546,13 @@
         <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3491</v>
+        <v>-0.6402</v>
       </c>
       <c r="T14" t="n">
-        <v>0.736</v>
+        <v>-0.1008</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0851</v>
+        <v>-0.5394</v>
       </c>
       <c r="V14" t="n">
         <v>2.6973</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.902</v>
+        <v>1.7039</v>
       </c>
       <c r="E15" t="n">
-        <v>3.569</v>
+        <v>4.092</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.667</v>
+        <v>-2.3881</v>
       </c>
       <c r="G15" t="n">
         <v>4.2274</v>
@@ -1624,13 +1624,13 @@
         <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2083</v>
+        <v>-1.4064</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0462</v>
+        <v>-0.5232</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1621</v>
+        <v>-0.8832</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5277</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5883</v>
+        <v>0.7647</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5928</v>
+        <v>5.9712</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0046</v>
+        <v>-5.2065</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0368</v>
+        <v>1.9547</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0261</v>
+        <v>-1.2554</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0107</v>
+        <v>3.2101</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6308</v>
+        <v>5.0554</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5518999999999999</v>
+        <v>-0.0092</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0789</v>
+        <v>5.0647</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.594</v>
+        <v>-3.1007</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5258</v>
+        <v>-1.2462</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0682</v>
+        <v>-1.8545</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4107</v>
+        <v>3.0801</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0111</v>
+        <v>-1.9469</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1899</v>
+        <v>-0.4147</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1787</v>
+        <v>-1.5321</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1786</v>
+        <v>-1.2965</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>2.3573</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-3.6538</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0499</v>
+        <v>0.3215</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9712</v>
+        <v>0.5928</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.9214</v>
+        <v>-0.2713</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9547</v>
+        <v>0.0368</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2554</v>
+        <v>0.0261</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2101</v>
+        <v>0.0107</v>
       </c>
       <c r="J17" t="n">
-        <v>5.0554</v>
+        <v>0.6308</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0092</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>5.0647</v>
+        <v>0.0789</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.1007</v>
+        <v>-0.594</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2462</v>
+        <v>-0.5258</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8545</v>
+        <v>-0.0682</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0534</v>
+        <v>-0.616</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>3.0801</v>
+        <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.6617</v>
+        <v>-0.2779</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4147</v>
+        <v>-0.1899</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.247</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2965</v>
+        <v>1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3573</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.6538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>V. MUÑOZ QUIÑONES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3098</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0932</v>
+        <v>3.0197</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.403</v>
+        <v>-2.9425</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1477</v>
+        <v>1.119</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7029</v>
+        <v>2.5659</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5552</v>
+        <v>-1.4468</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7911</v>
+        <v>3.4886</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0638</v>
+        <v>3.1729</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8549</v>
+        <v>0.3157</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9389</v>
+        <v>-2.3696</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6392</v>
+        <v>-0.6071</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2997</v>
+        <v>-1.7626</v>
       </c>
       <c r="P18" t="n">
-        <v>0.616</v>
+        <v>2.6694</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.616</v>
+        <v>2.6694</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2219</v>
+        <v>-2.1745</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3021</v>
+        <v>-0.4689</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-1.7056</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.5367</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.5367</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6637</v>
+        <v>-0.3952</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7059</v>
+        <v>0.7794</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3696</v>
+        <v>-1.1746</v>
       </c>
       <c r="G19" t="n">
-        <v>1.119</v>
+        <v>-1.1477</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5659</v>
+        <v>-1.7029</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4468</v>
+        <v>0.5552</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4886</v>
+        <v>0.7911</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1729</v>
+        <v>-1.0638</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3157</v>
+        <v>1.8549</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3696</v>
+        <v>-1.9389</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6071</v>
+        <v>-0.6392</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7626</v>
+        <v>-1.2997</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6694</v>
+        <v>0.616</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6694</v>
+        <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.9155</v>
+        <v>0.1365</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7827</v>
+        <v>-0.0117</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.1327</v>
+        <v>0.1482</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5367</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.5974</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6685</v>
+        <v>0.9823</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.414</v>
+        <v>-1.5797</v>
       </c>
       <c r="G20" t="n">
         <v>0.3342</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.703</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>1.0608</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6758</v>
+        <v>-1.7403</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9615</v>
+        <v>-1.2753</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7143</v>
+        <v>-0.465</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1163</v>
@@ -2092,13 +2092,13 @@
         <v>1.8481</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9961</v>
+        <v>-1.0606</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0464</v>
+        <v>-0.2674</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0424</v>
+        <v>-0.7931</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3581</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5163</v>
+        <v>-4.1223</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4684</v>
+        <v>-1.1546</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0478</v>
+        <v>-2.9676</v>
       </c>
       <c r="G22" t="n">
         <v>-1.491</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7214</v>
+        <v>-0.3274</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5928</v>
+        <v>-0.279</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1286</v>
+        <v>-0.0484</v>
       </c>
       <c r="V22" t="n">
         <v>-3.5359</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7277</v>
+        <v>-1.6357</v>
       </c>
       <c r="E23" t="n">
         <v>18.2257</v>
       </c>
       <c r="F23" t="n">
-        <v>-21.9535</v>
+        <v>-19.8614</v>
       </c>
       <c r="G23" t="n">
         <v>5.828100000000001</v>
@@ -2248,13 +2248,13 @@
         <v>15.4006</v>
       </c>
       <c r="S23" t="n">
-        <v>-10.3443</v>
+        <v>-8.2523</v>
       </c>
       <c r="T23" t="n">
         <v>-2.7323</v>
       </c>
       <c r="U23" t="n">
-        <v>-7.611999999999999</v>
+        <v>-5.5199</v>
       </c>
       <c r="V23" t="n">
         <v>-3.3182</v>
